--- a/src/ii_skills/shared/excel_templates/14_debt_benchmarking.xlsx
+++ b/src/ii_skills/shared/excel_templates/14_debt_benchmarking.xlsx
@@ -16,11 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,13 +29,19 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -45,18 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-        <bgColor rgb="00F0F0F0"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,30 +63,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,237 +443,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Debt_Type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Company_A_Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Company_A_Pct</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Company_B_Value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Company_B_Pct</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Subject_Value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Subject_Pct</t>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Debt Structure Comparison</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CMHC Insured</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>1631</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>598</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0.127</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Non-CMHC Insured</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>358</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>189</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>205</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>0.873</v>
-      </c>
-    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Unsecured Debt</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>450</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Debt Type</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Company A ($M)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>% Total</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Company B ($M)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>% Total</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Subject ($M)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>% Total</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Term Loan</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>149</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Senior Term Loan</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Credit Facility</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Revolver</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="F6" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Total Debt</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>3286</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>1270</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>234</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>1</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Subordinated Debt</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Credit Capacity</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>309</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0.277</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Undrawn Capacity</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>210</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>309</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>0.277</v>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
